--- a/artfynd/A 20807-2026 artfynd.xlsx
+++ b/artfynd/A 20807-2026 artfynd.xlsx
@@ -17038,7 +17038,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>134287405</v>
+        <v>134287415</v>
       </c>
       <c r="B162" t="n">
         <v>57975</v>
@@ -17073,10 +17073,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>556986</v>
+        <v>556176</v>
       </c>
       <c r="R162" t="n">
-        <v>7227897</v>
+        <v>7226987</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -17108,7 +17108,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17118,14 +17118,19 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>ny spår</t>
         </is>
       </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
       <c r="AE162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG162" t="b">
         <v>0</v>
@@ -17145,7 +17150,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>134287415</v>
+        <v>134287405</v>
       </c>
       <c r="B163" t="n">
         <v>57975</v>
@@ -17180,10 +17185,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>556176</v>
+        <v>556986</v>
       </c>
       <c r="R163" t="n">
-        <v>7226987</v>
+        <v>7227897</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -17215,7 +17220,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17225,19 +17230,14 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>ny spår</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
       <c r="AE163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG163" t="b">
         <v>0</v>
@@ -17792,10 +17792,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>134287402</v>
+        <v>134287403</v>
       </c>
       <c r="B169" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17803,21 +17803,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17827,10 +17827,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>557116</v>
+        <v>557113</v>
       </c>
       <c r="R169" t="n">
-        <v>7227864</v>
+        <v>7227865</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -17875,16 +17875,11 @@
           <t>14:11</t>
         </is>
       </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>osäker spår</t>
-        </is>
-      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
       <c r="AE169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG169" t="b">
         <v>0</v>
@@ -17904,7 +17899,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>134287406</v>
+        <v>134287402</v>
       </c>
       <c r="B170" t="n">
         <v>57975</v>
@@ -17939,10 +17934,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>556698</v>
+        <v>557116</v>
       </c>
       <c r="R170" t="n">
-        <v>7227566</v>
+        <v>7227864</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -17974,7 +17969,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -17984,7 +17979,12 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>osäker spår</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18118,10 +18118,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>134287403</v>
+        <v>134287406</v>
       </c>
       <c r="B172" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18129,21 +18129,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18153,10 +18153,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>557113</v>
+        <v>556698</v>
       </c>
       <c r="R172" t="n">
-        <v>7227865</v>
+        <v>7227566</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -18188,7 +18188,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18198,14 +18198,14 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD172" t="b">
         <v>0</v>
       </c>
       <c r="AE172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG172" t="b">
         <v>0</v>
@@ -18439,10 +18439,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>134287397</v>
+        <v>134287414</v>
       </c>
       <c r="B175" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18450,21 +18450,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18474,10 +18474,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>557008</v>
+        <v>556232</v>
       </c>
       <c r="R175" t="n">
-        <v>7227496</v>
+        <v>7227050</v>
       </c>
       <c r="S175" t="n">
         <v>5</v>
@@ -18509,7 +18509,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18519,7 +18519,12 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>två träd direkt bredvid. äldre spår</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18546,10 +18551,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>134287414</v>
+        <v>134287397</v>
       </c>
       <c r="B176" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18557,21 +18562,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18581,10 +18586,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>556232</v>
+        <v>557008</v>
       </c>
       <c r="R176" t="n">
-        <v>7227050</v>
+        <v>7227496</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -18616,7 +18621,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18626,12 +18631,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>två träd direkt bredvid. äldre spår</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD176" t="b">

--- a/artfynd/A 20807-2026 artfynd.xlsx
+++ b/artfynd/A 20807-2026 artfynd.xlsx
@@ -16707,10 +16707,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>134287400</v>
+        <v>134287398</v>
       </c>
       <c r="B159" t="n">
-        <v>57975</v>
+        <v>80481</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16718,21 +16718,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16742,13 +16742,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>557196</v>
+        <v>557019</v>
       </c>
       <c r="R159" t="n">
-        <v>7227820</v>
+        <v>7227511</v>
       </c>
       <c r="S159" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -16787,19 +16787,14 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>osäker fynd</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG159" t="b">
         <v>0</v>
@@ -16819,10 +16814,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>134287398</v>
+        <v>134287400</v>
       </c>
       <c r="B160" t="n">
-        <v>80474</v>
+        <v>57975</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16830,21 +16825,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16854,13 +16849,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>557019</v>
+        <v>557196</v>
       </c>
       <c r="R160" t="n">
-        <v>7227511</v>
+        <v>7227820</v>
       </c>
       <c r="S160" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16889,7 +16884,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -16899,14 +16894,19 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>osäker fynd</t>
         </is>
       </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG160" t="b">
         <v>0</v>
@@ -17038,7 +17038,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>134287415</v>
+        <v>134287405</v>
       </c>
       <c r="B162" t="n">
         <v>57975</v>
@@ -17073,10 +17073,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>556176</v>
+        <v>556986</v>
       </c>
       <c r="R162" t="n">
-        <v>7226987</v>
+        <v>7227897</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -17108,7 +17108,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17118,19 +17118,14 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>ny spår</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
       <c r="AE162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG162" t="b">
         <v>0</v>
@@ -17150,7 +17145,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>134287405</v>
+        <v>134287415</v>
       </c>
       <c r="B163" t="n">
         <v>57975</v>
@@ -17185,10 +17180,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>556986</v>
+        <v>556176</v>
       </c>
       <c r="R163" t="n">
-        <v>7227897</v>
+        <v>7226987</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -17220,7 +17215,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17230,14 +17225,19 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>ny spår</t>
         </is>
       </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
       <c r="AE163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG163" t="b">
         <v>0</v>
@@ -17688,7 +17688,7 @@
         <v>134287418</v>
       </c>
       <c r="B168" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17792,10 +17792,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>134287403</v>
+        <v>134287402</v>
       </c>
       <c r="B169" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17803,21 +17803,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17827,10 +17827,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>557113</v>
+        <v>557116</v>
       </c>
       <c r="R169" t="n">
-        <v>7227865</v>
+        <v>7227864</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -17875,11 +17875,16 @@
           <t>14:11</t>
         </is>
       </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>osäker spår</t>
+        </is>
+      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
       <c r="AE169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG169" t="b">
         <v>0</v>
@@ -17899,7 +17904,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>134287402</v>
+        <v>134287406</v>
       </c>
       <c r="B170" t="n">
         <v>57975</v>
@@ -17934,10 +17939,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>557116</v>
+        <v>556698</v>
       </c>
       <c r="R170" t="n">
-        <v>7227864</v>
+        <v>7227566</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -17969,7 +17974,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -17979,12 +17984,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>osäker spår</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18014,7 +18014,7 @@
         <v>134287417</v>
       </c>
       <c r="B171" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18118,10 +18118,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>134287406</v>
+        <v>134287403</v>
       </c>
       <c r="B172" t="n">
-        <v>57975</v>
+        <v>79366</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18129,21 +18129,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18153,10 +18153,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>556698</v>
+        <v>557113</v>
       </c>
       <c r="R172" t="n">
-        <v>7227566</v>
+        <v>7227865</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -18188,7 +18188,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18198,14 +18198,14 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD172" t="b">
         <v>0</v>
       </c>
       <c r="AE172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG172" t="b">
         <v>0</v>
@@ -18439,10 +18439,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>134287414</v>
+        <v>134287397</v>
       </c>
       <c r="B175" t="n">
-        <v>57975</v>
+        <v>79366</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18450,21 +18450,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18474,10 +18474,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>556232</v>
+        <v>557008</v>
       </c>
       <c r="R175" t="n">
-        <v>7227050</v>
+        <v>7227496</v>
       </c>
       <c r="S175" t="n">
         <v>5</v>
@@ -18509,7 +18509,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18519,12 +18519,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>två träd direkt bredvid. äldre spår</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18551,10 +18546,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>134287397</v>
+        <v>134287414</v>
       </c>
       <c r="B176" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18562,21 +18557,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18586,10 +18581,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>557008</v>
+        <v>556232</v>
       </c>
       <c r="R176" t="n">
-        <v>7227496</v>
+        <v>7227050</v>
       </c>
       <c r="S176" t="n">
         <v>5</v>
@@ -18621,7 +18616,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18631,7 +18626,12 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>två träd direkt bredvid. äldre spår</t>
         </is>
       </c>
       <c r="AD176" t="b">
